--- a/summary_stats/chuuchuu_summary_2025_05.xlsx
+++ b/summary_stats/chuuchuu_summary_2025_05.xlsx
@@ -585,16 +585,16 @@
         <v>21</v>
       </c>
       <c r="N2" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O2" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q2" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="R2" t="n">
         <v>23</v>
@@ -1454,25 +1454,25 @@
         <v>88</v>
       </c>
       <c r="N13" t="n">
-        <v>1035</v>
+        <v>1008</v>
       </c>
       <c r="O13" t="n">
-        <v>840</v>
+        <v>814</v>
       </c>
       <c r="P13" t="n">
-        <v>766</v>
+        <v>740</v>
       </c>
       <c r="Q13" t="n">
-        <v>599</v>
+        <v>574</v>
       </c>
       <c r="R13" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="S13" t="n">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="T13" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="U13" t="n">
         <v>2047</v>
@@ -1691,25 +1691,25 @@
         <v>8</v>
       </c>
       <c r="N16" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="O16" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P16" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="Q16" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="R16" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="S16" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="T16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="U16" t="n">
         <v>355</v>
@@ -1770,25 +1770,25 @@
         <v>718</v>
       </c>
       <c r="N17" t="n">
-        <v>2318</v>
+        <v>2027</v>
       </c>
       <c r="O17" t="n">
-        <v>1971</v>
+        <v>1708</v>
       </c>
       <c r="P17" t="n">
-        <v>1838</v>
+        <v>1584</v>
       </c>
       <c r="Q17" t="n">
-        <v>1431</v>
+        <v>1217</v>
       </c>
       <c r="R17" t="n">
-        <v>1059</v>
+        <v>881</v>
       </c>
       <c r="S17" t="n">
-        <v>483</v>
+        <v>367</v>
       </c>
       <c r="T17" t="n">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="U17" t="n">
         <v>3807</v>
@@ -1849,25 +1849,25 @@
         <v>97</v>
       </c>
       <c r="N18" t="n">
-        <v>898</v>
+        <v>863</v>
       </c>
       <c r="O18" t="n">
-        <v>731</v>
+        <v>698</v>
       </c>
       <c r="P18" t="n">
-        <v>667</v>
+        <v>634</v>
       </c>
       <c r="Q18" t="n">
-        <v>486</v>
+        <v>454</v>
       </c>
       <c r="R18" t="n">
-        <v>350</v>
+        <v>320</v>
       </c>
       <c r="S18" t="n">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="T18" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="U18" t="n">
         <v>2066</v>
@@ -1928,25 +1928,25 @@
         <v>1622</v>
       </c>
       <c r="N19" t="n">
-        <v>8450</v>
+        <v>7913</v>
       </c>
       <c r="O19" t="n">
-        <v>7290</v>
+        <v>6780</v>
       </c>
       <c r="P19" t="n">
-        <v>6823</v>
+        <v>6323</v>
       </c>
       <c r="Q19" t="n">
-        <v>5394</v>
+        <v>4949</v>
       </c>
       <c r="R19" t="n">
-        <v>4197</v>
+        <v>3807</v>
       </c>
       <c r="S19" t="n">
-        <v>2209</v>
+        <v>1910</v>
       </c>
       <c r="T19" t="n">
-        <v>649</v>
+        <v>516</v>
       </c>
       <c r="U19" t="n">
         <v>13920</v>
@@ -2007,25 +2007,25 @@
         <v>242</v>
       </c>
       <c r="N20" t="n">
-        <v>2417</v>
+        <v>2304</v>
       </c>
       <c r="O20" t="n">
-        <v>2141</v>
+        <v>2031</v>
       </c>
       <c r="P20" t="n">
-        <v>2047</v>
+        <v>1940</v>
       </c>
       <c r="Q20" t="n">
-        <v>1681</v>
+        <v>1584</v>
       </c>
       <c r="R20" t="n">
-        <v>1349</v>
+        <v>1266</v>
       </c>
       <c r="S20" t="n">
-        <v>696</v>
+        <v>635</v>
       </c>
       <c r="T20" t="n">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="U20" t="n">
         <v>3458</v>
@@ -2244,22 +2244,22 @@
         <v>2</v>
       </c>
       <c r="N23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -2323,25 +2323,25 @@
         <v>58</v>
       </c>
       <c r="N24" t="n">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="O24" t="n">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="P24" t="n">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="Q24" t="n">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="R24" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="S24" t="n">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="T24" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="U24" t="n">
         <v>553</v>
@@ -2402,22 +2402,22 @@
         <v>36</v>
       </c>
       <c r="N25" t="n">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="O25" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="P25" t="n">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="Q25" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="R25" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="S25" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="T25" t="n">
         <v>4</v>
@@ -2560,22 +2560,22 @@
         <v>10</v>
       </c>
       <c r="N27" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O27" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P27" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q27" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R27" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T27" t="n">
         <v>8</v>
@@ -3113,25 +3113,25 @@
         <v>306</v>
       </c>
       <c r="N34" t="n">
-        <v>868</v>
+        <v>819</v>
       </c>
       <c r="O34" t="n">
-        <v>862</v>
+        <v>813</v>
       </c>
       <c r="P34" t="n">
-        <v>856</v>
+        <v>808</v>
       </c>
       <c r="Q34" t="n">
-        <v>666</v>
+        <v>626</v>
       </c>
       <c r="R34" t="n">
-        <v>531</v>
+        <v>495</v>
       </c>
       <c r="S34" t="n">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="T34" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="U34" t="n">
         <v>3565</v>
@@ -3192,25 +3192,25 @@
         <v>32</v>
       </c>
       <c r="N35" t="n">
-        <v>352</v>
+        <v>330</v>
       </c>
       <c r="O35" t="n">
-        <v>315</v>
+        <v>294</v>
       </c>
       <c r="P35" t="n">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="Q35" t="n">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="R35" t="n">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="S35" t="n">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="T35" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="U35" t="n">
         <v>550</v>
@@ -3271,25 +3271,25 @@
         <v>12</v>
       </c>
       <c r="N36" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="O36" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="P36" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="Q36" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R36" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T36" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U36" t="n">
         <v>57</v>
@@ -4219,19 +4219,19 @@
         <v>14</v>
       </c>
       <c r="N48" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O48" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P48" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q48" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R48" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -4298,22 +4298,22 @@
         <v>2967</v>
       </c>
       <c r="N49" t="n">
-        <v>4077</v>
+        <v>3944</v>
       </c>
       <c r="O49" t="n">
-        <v>2267</v>
+        <v>2177</v>
       </c>
       <c r="P49" t="n">
-        <v>1786</v>
+        <v>1704</v>
       </c>
       <c r="Q49" t="n">
-        <v>925</v>
+        <v>863</v>
       </c>
       <c r="R49" t="n">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="S49" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="T49" t="n">
         <v>2</v>
@@ -4377,25 +4377,25 @@
         <v>24</v>
       </c>
       <c r="N50" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="O50" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="P50" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="Q50" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="R50" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="S50" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="T50" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="U50" t="n">
         <v>481</v>
@@ -4456,22 +4456,22 @@
         <v>609</v>
       </c>
       <c r="N51" t="n">
-        <v>465</v>
+        <v>422</v>
       </c>
       <c r="O51" t="n">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="P51" t="n">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="Q51" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="R51" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="S51" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T51" t="n">
         <v>0</v>
@@ -4535,25 +4535,25 @@
         <v>10</v>
       </c>
       <c r="N52" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="O52" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="P52" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="Q52" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="R52" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="S52" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="T52" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="U52" t="n">
         <v>461</v>
@@ -4614,25 +4614,25 @@
         <v>7</v>
       </c>
       <c r="N53" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O53" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P53" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q53" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="R53" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S53" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U53" t="n">
         <v>180</v>
@@ -4772,13 +4772,13 @@
         <v>97</v>
       </c>
       <c r="N55" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="O55" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P55" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q55" t="n">
         <v>52</v>
@@ -4851,19 +4851,19 @@
         <v>2911</v>
       </c>
       <c r="N56" t="n">
-        <v>4932</v>
+        <v>4842</v>
       </c>
       <c r="O56" t="n">
-        <v>2345</v>
+        <v>2299</v>
       </c>
       <c r="P56" t="n">
-        <v>1727</v>
+        <v>1689</v>
       </c>
       <c r="Q56" t="n">
-        <v>685</v>
+        <v>670</v>
       </c>
       <c r="R56" t="n">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="S56" t="n">
         <v>28</v>
@@ -4930,16 +4930,16 @@
         <v>1064</v>
       </c>
       <c r="N57" t="n">
-        <v>2320</v>
+        <v>2282</v>
       </c>
       <c r="O57" t="n">
-        <v>896</v>
+        <v>875</v>
       </c>
       <c r="P57" t="n">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="Q57" t="n">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="R57" t="n">
         <v>88</v>
@@ -5009,16 +5009,16 @@
         <v>94</v>
       </c>
       <c r="N58" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="O58" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="P58" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Q58" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R58" t="n">
         <v>25</v>
@@ -5957,22 +5957,22 @@
         <v>351</v>
       </c>
       <c r="N70" t="n">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="O70" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="P70" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="Q70" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="R70" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="S70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T70" t="n">
         <v>1</v>
@@ -6115,22 +6115,22 @@
         <v>158</v>
       </c>
       <c r="N72" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="O72" t="n">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="P72" t="n">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="Q72" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="R72" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="S72" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="T72" t="n">
         <v>10</v>
@@ -6194,19 +6194,19 @@
         <v>61</v>
       </c>
       <c r="N73" t="n">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="O73" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="P73" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="Q73" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="R73" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="S73" t="n">
         <v>36</v>
@@ -6510,19 +6510,19 @@
         <v>36</v>
       </c>
       <c r="N77" t="n">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="O77" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="P77" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Q77" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="R77" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="S77" t="n">
         <v>86</v>
@@ -7300,25 +7300,25 @@
         <v>41</v>
       </c>
       <c r="N87" t="n">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="O87" t="n">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="P87" t="n">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="Q87" t="n">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="R87" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="S87" t="n">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="T87" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U87" t="n">
         <v>1834</v>
@@ -7379,25 +7379,25 @@
         <v>14</v>
       </c>
       <c r="N88" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="O88" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="P88" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="Q88" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="R88" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="S88" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T88" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="U88" t="n">
         <v>246</v>
@@ -7853,22 +7853,22 @@
         <v>288</v>
       </c>
       <c r="N94" t="n">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="O94" t="n">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="P94" t="n">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="Q94" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="R94" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="S94" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T94" t="n">
         <v>8</v>
@@ -8722,19 +8722,19 @@
         <v>44</v>
       </c>
       <c r="N105" t="n">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="O105" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="P105" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="Q105" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="R105" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S105" t="n">
         <v>4</v>
@@ -8801,22 +8801,22 @@
         <v>12</v>
       </c>
       <c r="N106" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="O106" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="P106" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="Q106" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="R106" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="T106" t="n">
         <v>2</v>
@@ -8880,25 +8880,25 @@
         <v>861</v>
       </c>
       <c r="N107" t="n">
-        <v>5539</v>
+        <v>5395</v>
       </c>
       <c r="O107" t="n">
-        <v>3364</v>
+        <v>3249</v>
       </c>
       <c r="P107" t="n">
-        <v>2759</v>
+        <v>2661</v>
       </c>
       <c r="Q107" t="n">
-        <v>1384</v>
+        <v>1322</v>
       </c>
       <c r="R107" t="n">
-        <v>716</v>
+        <v>673</v>
       </c>
       <c r="S107" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="T107" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U107" t="n">
         <v>27593</v>
@@ -8959,22 +8959,22 @@
         <v>58</v>
       </c>
       <c r="N108" t="n">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="O108" t="n">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="P108" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="Q108" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="R108" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="S108" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="T108" t="n">
         <v>0</v>
@@ -9117,22 +9117,22 @@
         <v>19</v>
       </c>
       <c r="N110" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="O110" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="P110" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="Q110" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="R110" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="S110" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T110" t="n">
         <v>8</v>
@@ -9196,22 +9196,22 @@
         <v>162</v>
       </c>
       <c r="N111" t="n">
-        <v>2626</v>
+        <v>2609</v>
       </c>
       <c r="O111" t="n">
-        <v>1397</v>
+        <v>1384</v>
       </c>
       <c r="P111" t="n">
-        <v>1078</v>
+        <v>1068</v>
       </c>
       <c r="Q111" t="n">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="R111" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="S111" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="T111" t="n">
         <v>2</v>
@@ -9275,25 +9275,25 @@
         <v>48</v>
       </c>
       <c r="N112" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="O112" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="P112" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="Q112" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="R112" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="S112" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U112" t="n">
         <v>4232</v>
@@ -9591,22 +9591,22 @@
         <v>60</v>
       </c>
       <c r="N116" t="n">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="O116" t="n">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="P116" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="Q116" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="R116" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="S116" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T116" t="n">
         <v>1</v>
@@ -9670,10 +9670,10 @@
         <v>3</v>
       </c>
       <c r="N117" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O117" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P117" t="n">
         <v>3</v>
@@ -9749,25 +9749,25 @@
         <v>497</v>
       </c>
       <c r="N118" t="n">
-        <v>3803</v>
+        <v>3750</v>
       </c>
       <c r="O118" t="n">
-        <v>2107</v>
+        <v>2069</v>
       </c>
       <c r="P118" t="n">
-        <v>1650</v>
+        <v>1617</v>
       </c>
       <c r="Q118" t="n">
-        <v>768</v>
+        <v>748</v>
       </c>
       <c r="R118" t="n">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="S118" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="T118" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U118" t="n">
         <v>27231</v>
@@ -9828,22 +9828,22 @@
         <v>122</v>
       </c>
       <c r="N119" t="n">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="O119" t="n">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="P119" t="n">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="Q119" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="R119" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="S119" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T119" t="n">
         <v>0</v>
@@ -10223,22 +10223,22 @@
         <v>29</v>
       </c>
       <c r="N124" t="n">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="O124" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="P124" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="Q124" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="R124" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="S124" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T124" t="n">
         <v>0</v>
@@ -10539,25 +10539,25 @@
         <v>54</v>
       </c>
       <c r="N128" t="n">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="O128" t="n">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="P128" t="n">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="Q128" t="n">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="R128" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="S128" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="T128" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="U128" t="n">
         <v>1881</v>
@@ -10855,22 +10855,22 @@
         <v>4</v>
       </c>
       <c r="N132" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O132" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P132" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q132" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R132" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S132" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T132" t="n">
         <v>10</v>
@@ -11171,25 +11171,25 @@
         <v>159</v>
       </c>
       <c r="N136" t="n">
-        <v>2785</v>
+        <v>2741</v>
       </c>
       <c r="O136" t="n">
-        <v>1599</v>
+        <v>1559</v>
       </c>
       <c r="P136" t="n">
-        <v>1599</v>
+        <v>1559</v>
       </c>
       <c r="Q136" t="n">
-        <v>1067</v>
+        <v>1031</v>
       </c>
       <c r="R136" t="n">
-        <v>808</v>
+        <v>779</v>
       </c>
       <c r="S136" t="n">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="T136" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="U136" t="n">
         <v>13442</v>
@@ -11250,25 +11250,25 @@
         <v>9</v>
       </c>
       <c r="N137" t="n">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="O137" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="P137" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="Q137" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="R137" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="S137" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="T137" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="U137" t="n">
         <v>946</v>
@@ -11961,25 +11961,25 @@
         <v>13</v>
       </c>
       <c r="N146" t="n">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="O146" t="n">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P146" t="n">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="Q146" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R146" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="S146" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="T146" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="U146" t="n">
         <v>1519</v>
@@ -12119,10 +12119,10 @@
         <v>25</v>
       </c>
       <c r="N148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P148" t="n">
         <v>2</v>
@@ -12435,25 +12435,25 @@
         <v>27</v>
       </c>
       <c r="N152" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="O152" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="P152" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="Q152" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="R152" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="S152" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T152" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="U152" t="n">
         <v>490</v>
@@ -12514,25 +12514,25 @@
         <v>8</v>
       </c>
       <c r="N153" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O153" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P153" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q153" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R153" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S153" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T153" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="U153" t="n">
         <v>294</v>
@@ -12593,25 +12593,25 @@
         <v>205</v>
       </c>
       <c r="N154" t="n">
-        <v>3184</v>
+        <v>3174</v>
       </c>
       <c r="O154" t="n">
-        <v>2537</v>
+        <v>2529</v>
       </c>
       <c r="P154" t="n">
-        <v>2260</v>
+        <v>2253</v>
       </c>
       <c r="Q154" t="n">
-        <v>1603</v>
+        <v>1596</v>
       </c>
       <c r="R154" t="n">
-        <v>1167</v>
+        <v>1160</v>
       </c>
       <c r="S154" t="n">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="T154" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="U154" t="n">
         <v>6931</v>
@@ -12672,25 +12672,25 @@
         <v>125</v>
       </c>
       <c r="N155" t="n">
-        <v>1216</v>
+        <v>1202</v>
       </c>
       <c r="O155" t="n">
-        <v>979</v>
+        <v>970</v>
       </c>
       <c r="P155" t="n">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="Q155" t="n">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="R155" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="S155" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="T155" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="U155" t="n">
         <v>3042</v>
@@ -12988,22 +12988,22 @@
         <v>457</v>
       </c>
       <c r="N159" t="n">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="O159" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="P159" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q159" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="R159" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S159" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T159" t="n">
         <v>4</v>
@@ -13383,25 +13383,25 @@
         <v>11644</v>
       </c>
       <c r="N164" t="n">
-        <v>47552</v>
+        <v>46943</v>
       </c>
       <c r="O164" t="n">
-        <v>27622</v>
+        <v>27133</v>
       </c>
       <c r="P164" t="n">
-        <v>22193</v>
+        <v>21749</v>
       </c>
       <c r="Q164" t="n">
-        <v>11714</v>
+        <v>11403</v>
       </c>
       <c r="R164" t="n">
-        <v>7067</v>
+        <v>6838</v>
       </c>
       <c r="S164" t="n">
-        <v>2442</v>
+        <v>2332</v>
       </c>
       <c r="T164" t="n">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="U164" t="n">
         <v>223270</v>
@@ -13462,19 +13462,19 @@
         <v>236</v>
       </c>
       <c r="N165" t="n">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="O165" t="n">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="P165" t="n">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="Q165" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R165" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="S165" t="n">
         <v>22</v>
@@ -14726,25 +14726,25 @@
         <v>4</v>
       </c>
       <c r="N181" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O181" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P181" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Q181" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R181" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S181" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U181" t="n">
         <v>24</v>
@@ -15038,13 +15038,13 @@
         <v>3</v>
       </c>
       <c r="N185" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O185" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P185" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q185" t="n">
         <v>52</v>
@@ -15984,22 +15984,22 @@
         <v>4</v>
       </c>
       <c r="O7" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P7" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q7" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="R7" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="S7" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="T7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U7" t="n">
         <v>10</v>
@@ -16236,22 +16236,22 @@
         <v>29</v>
       </c>
       <c r="O10" t="n">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="P10" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="Q10" t="n">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="R10" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="S10" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -16488,25 +16488,25 @@
         <v>54</v>
       </c>
       <c r="O13" t="n">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="P13" t="n">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="Q13" t="n">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="R13" t="n">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="S13" t="n">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="T13" t="n">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="U13" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="V13" t="n">
         <v>1881</v>
@@ -16824,25 +16824,25 @@
         <v>159</v>
       </c>
       <c r="O17" t="n">
-        <v>2785</v>
+        <v>2741</v>
       </c>
       <c r="P17" t="n">
-        <v>1599</v>
+        <v>1559</v>
       </c>
       <c r="Q17" t="n">
-        <v>1599</v>
+        <v>1559</v>
       </c>
       <c r="R17" t="n">
-        <v>1067</v>
+        <v>1031</v>
       </c>
       <c r="S17" t="n">
-        <v>808</v>
+        <v>779</v>
       </c>
       <c r="T17" t="n">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="U17" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="V17" t="n">
         <v>13442</v>
@@ -16908,25 +16908,25 @@
         <v>9</v>
       </c>
       <c r="O18" t="n">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="P18" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="Q18" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="R18" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="S18" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="T18" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="U18" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="V18" t="n">
         <v>890</v>
@@ -17202,25 +17202,25 @@
         <v>28</v>
       </c>
       <c r="O2" t="n">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="P2" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="Q2" t="n">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="R2" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="S2" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="T2" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="U2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V2" t="n">
         <v>330</v>
@@ -17454,19 +17454,19 @@
         <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="n">
         <v>3</v>
@@ -17706,22 +17706,22 @@
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U8" t="n">
         <v>2</v>
@@ -17790,25 +17790,25 @@
         <v>6</v>
       </c>
       <c r="O9" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Q9" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="R9" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="S9" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="T9" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="U9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V9" t="n">
         <v>59</v>
@@ -17874,25 +17874,25 @@
         <v>6</v>
       </c>
       <c r="O10" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P10" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Q10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="R10" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="S10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="T10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="U10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V10" t="n">
         <v>57</v>
@@ -18126,25 +18126,25 @@
         <v>718</v>
       </c>
       <c r="O13" t="n">
-        <v>2309</v>
+        <v>2018</v>
       </c>
       <c r="P13" t="n">
-        <v>1967</v>
+        <v>1704</v>
       </c>
       <c r="Q13" t="n">
-        <v>1836</v>
+        <v>1582</v>
       </c>
       <c r="R13" t="n">
-        <v>1429</v>
+        <v>1215</v>
       </c>
       <c r="S13" t="n">
-        <v>1057</v>
+        <v>879</v>
       </c>
       <c r="T13" t="n">
-        <v>483</v>
+        <v>367</v>
       </c>
       <c r="U13" t="n">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="V13" t="n">
         <v>3785</v>
@@ -18210,25 +18210,25 @@
         <v>43</v>
       </c>
       <c r="O14" t="n">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="P14" t="n">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="Q14" t="n">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="R14" t="n">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="S14" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="T14" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="U14" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="V14" t="n">
         <v>491</v>
@@ -18294,25 +18294,25 @@
         <v>1621</v>
       </c>
       <c r="O15" t="n">
-        <v>8450</v>
+        <v>7913</v>
       </c>
       <c r="P15" t="n">
-        <v>7290</v>
+        <v>6780</v>
       </c>
       <c r="Q15" t="n">
-        <v>6823</v>
+        <v>6323</v>
       </c>
       <c r="R15" t="n">
-        <v>5394</v>
+        <v>4949</v>
       </c>
       <c r="S15" t="n">
-        <v>4197</v>
+        <v>3807</v>
       </c>
       <c r="T15" t="n">
-        <v>2209</v>
+        <v>1910</v>
       </c>
       <c r="U15" t="n">
-        <v>649</v>
+        <v>516</v>
       </c>
       <c r="V15" t="n">
         <v>13920</v>
@@ -19050,25 +19050,25 @@
         <v>24</v>
       </c>
       <c r="O24" t="n">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="P24" t="n">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="Q24" t="n">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="R24" t="n">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="S24" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="T24" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="U24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V24" t="n">
         <v>455</v>
@@ -19302,25 +19302,25 @@
         <v>5</v>
       </c>
       <c r="O27" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="P27" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="Q27" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="R27" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="S27" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="T27" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="U27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V27" t="n">
         <v>277</v>
@@ -19386,25 +19386,25 @@
         <v>46</v>
       </c>
       <c r="O28" t="n">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="P28" t="n">
-        <v>384</v>
+        <v>363</v>
       </c>
       <c r="Q28" t="n">
-        <v>361</v>
+        <v>340</v>
       </c>
       <c r="R28" t="n">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="S28" t="n">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="T28" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="U28" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="V28" t="n">
         <v>617</v>
@@ -19470,22 +19470,22 @@
         <v>11</v>
       </c>
       <c r="O29" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="P29" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="Q29" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="R29" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="T29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
@@ -19554,25 +19554,25 @@
         <v>7</v>
       </c>
       <c r="O30" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="P30" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Q30" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="R30" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S30" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="T30" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="U30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="V30" t="n">
         <v>236</v>
@@ -19806,22 +19806,22 @@
         <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P33" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q33" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R33" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="S33" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U33" t="n">
         <v>2</v>
@@ -19890,19 +19890,19 @@
         <v>17</v>
       </c>
       <c r="O34" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P34" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q34" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R34" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S34" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="T34" t="n">
         <v>13</v>
@@ -20142,25 +20142,25 @@
         <v>19</v>
       </c>
       <c r="O37" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="P37" t="n">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="Q37" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="R37" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="S37" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="T37" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="U37" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="V37" t="n">
         <v>78</v>
@@ -20226,25 +20226,25 @@
         <v>26</v>
       </c>
       <c r="O38" t="n">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="P38" t="n">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="Q38" t="n">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="R38" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="S38" t="n">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="T38" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="U38" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="V38" t="n">
         <v>341</v>
@@ -20310,25 +20310,25 @@
         <v>138</v>
       </c>
       <c r="O39" t="n">
-        <v>941</v>
+        <v>869</v>
       </c>
       <c r="P39" t="n">
-        <v>858</v>
+        <v>789</v>
       </c>
       <c r="Q39" t="n">
-        <v>817</v>
+        <v>750</v>
       </c>
       <c r="R39" t="n">
-        <v>710</v>
+        <v>650</v>
       </c>
       <c r="S39" t="n">
-        <v>576</v>
+        <v>523</v>
       </c>
       <c r="T39" t="n">
-        <v>309</v>
+        <v>272</v>
       </c>
       <c r="U39" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="V39" t="n">
         <v>1311</v>
@@ -20478,25 +20478,25 @@
         <v>22</v>
       </c>
       <c r="O41" t="n">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="P41" t="n">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="Q41" t="n">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="R41" t="n">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="S41" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="T41" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="U41" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V41" t="n">
         <v>449</v>
@@ -20646,25 +20646,25 @@
         <v>11</v>
       </c>
       <c r="O43" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="P43" t="n">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="Q43" t="n">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="R43" t="n">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="S43" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="T43" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="V43" t="n">
         <v>613</v>
@@ -20982,22 +20982,22 @@
         <v>2</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -21066,25 +21066,25 @@
         <v>58</v>
       </c>
       <c r="O48" t="n">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="P48" t="n">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="Q48" t="n">
-        <v>306</v>
+        <v>285</v>
       </c>
       <c r="R48" t="n">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="S48" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="T48" t="n">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="U48" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="V48" t="n">
         <v>553</v>
@@ -21234,22 +21234,22 @@
         <v>10</v>
       </c>
       <c r="O50" t="n">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P50" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q50" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R50" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S50" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T50" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U50" t="n">
         <v>8</v>
@@ -21402,22 +21402,22 @@
         <v>21</v>
       </c>
       <c r="O52" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="P52" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q52" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="R52" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="S52" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="T52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U52" t="n">
         <v>3</v>
@@ -21948,25 +21948,25 @@
         <v>23</v>
       </c>
       <c r="O2" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P2" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q2" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R2" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="S2" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="T2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V2" t="n">
         <v>419</v>
@@ -22032,25 +22032,25 @@
         <v>10</v>
       </c>
       <c r="O3" t="n">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="P3" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="Q3" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="R3" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="S3" t="n">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="T3" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="U3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="V3" t="n">
         <v>461</v>
@@ -22116,25 +22116,25 @@
         <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V4" t="n">
         <v>62</v>
@@ -22284,22 +22284,22 @@
         <v>2967</v>
       </c>
       <c r="O6" t="n">
-        <v>4077</v>
+        <v>3944</v>
       </c>
       <c r="P6" t="n">
-        <v>2267</v>
+        <v>2177</v>
       </c>
       <c r="Q6" t="n">
-        <v>1786</v>
+        <v>1704</v>
       </c>
       <c r="R6" t="n">
-        <v>925</v>
+        <v>863</v>
       </c>
       <c r="S6" t="n">
-        <v>436</v>
+        <v>395</v>
       </c>
       <c r="T6" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="U6" t="n">
         <v>2</v>
@@ -22368,22 +22368,22 @@
         <v>609</v>
       </c>
       <c r="O7" t="n">
-        <v>465</v>
+        <v>422</v>
       </c>
       <c r="P7" t="n">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="Q7" t="n">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="R7" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="S7" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="T7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -22536,13 +22536,13 @@
         <v>97</v>
       </c>
       <c r="O9" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="P9" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="Q9" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R9" t="n">
         <v>52</v>
@@ -22620,19 +22620,19 @@
         <v>2911</v>
       </c>
       <c r="O10" t="n">
-        <v>4932</v>
+        <v>4842</v>
       </c>
       <c r="P10" t="n">
-        <v>2345</v>
+        <v>2299</v>
       </c>
       <c r="Q10" t="n">
-        <v>1727</v>
+        <v>1689</v>
       </c>
       <c r="R10" t="n">
-        <v>685</v>
+        <v>670</v>
       </c>
       <c r="S10" t="n">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="T10" t="n">
         <v>28</v>
@@ -22704,16 +22704,16 @@
         <v>1064</v>
       </c>
       <c r="O11" t="n">
-        <v>2320</v>
+        <v>2282</v>
       </c>
       <c r="P11" t="n">
-        <v>896</v>
+        <v>875</v>
       </c>
       <c r="Q11" t="n">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="R11" t="n">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="S11" t="n">
         <v>88</v>
@@ -22872,19 +22872,19 @@
         <v>14</v>
       </c>
       <c r="O13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="P13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="S13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T13" t="n">
         <v>5</v>
@@ -22956,25 +22956,25 @@
         <v>7</v>
       </c>
       <c r="O14" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P14" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q14" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R14" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S14" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T14" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="U14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V14" t="n">
         <v>180</v>
@@ -25938,16 +25938,16 @@
         <v>94</v>
       </c>
       <c r="O35" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P35" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="Q35" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="R35" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -26526,22 +26526,22 @@
         <v>351</v>
       </c>
       <c r="O42" t="n">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="P42" t="n">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="Q42" t="n">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="R42" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="S42" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>1</v>
@@ -26694,22 +26694,22 @@
         <v>158</v>
       </c>
       <c r="O44" t="n">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="P44" t="n">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="Q44" t="n">
-        <v>154</v>
+        <v>135</v>
       </c>
       <c r="R44" t="n">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="S44" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="T44" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U44" t="n">
         <v>10</v>
@@ -26778,19 +26778,19 @@
         <v>61</v>
       </c>
       <c r="O45" t="n">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="P45" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="Q45" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="R45" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="S45" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T45" t="n">
         <v>34</v>
@@ -27660,25 +27660,25 @@
         <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="P4" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="Q4" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="R4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="S4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="U4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V4" t="n">
         <v>308</v>
@@ -28080,22 +28080,22 @@
         <v>288</v>
       </c>
       <c r="O9" t="n">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="P9" t="n">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="Q9" t="n">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="R9" t="n">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="S9" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="T9" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="U9" t="n">
         <v>8</v>
@@ -28752,22 +28752,22 @@
         <v>11</v>
       </c>
       <c r="O17" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="P17" t="n">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="Q17" t="n">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="R17" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="S17" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="T17" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="U17" t="n">
         <v>7</v>
@@ -28836,25 +28836,25 @@
         <v>8</v>
       </c>
       <c r="O18" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="P18" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="Q18" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="R18" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="S18" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="T18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="U18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="V18" t="n">
         <v>190</v>
@@ -29844,7 +29844,7 @@
         <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P30" t="n">
         <v>35</v>
@@ -29928,13 +29928,13 @@
         <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R31" t="n">
         <v>5</v>
@@ -30222,22 +30222,22 @@
         <v>19</v>
       </c>
       <c r="O2" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="P2" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="Q2" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="R2" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="S2" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="T2" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="U2" t="n">
         <v>8</v>
@@ -30306,19 +30306,19 @@
         <v>44</v>
       </c>
       <c r="O3" t="n">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="P3" t="n">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="Q3" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="R3" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="S3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T3" t="n">
         <v>4</v>
@@ -30390,22 +30390,22 @@
         <v>12</v>
       </c>
       <c r="O4" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="P4" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="Q4" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="R4" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="S4" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="T4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="U4" t="n">
         <v>2</v>
@@ -30642,25 +30642,25 @@
         <v>861</v>
       </c>
       <c r="O7" t="n">
-        <v>5539</v>
+        <v>5395</v>
       </c>
       <c r="P7" t="n">
-        <v>3364</v>
+        <v>3249</v>
       </c>
       <c r="Q7" t="n">
-        <v>2759</v>
+        <v>2661</v>
       </c>
       <c r="R7" t="n">
-        <v>1384</v>
+        <v>1322</v>
       </c>
       <c r="S7" t="n">
-        <v>716</v>
+        <v>673</v>
       </c>
       <c r="T7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="U7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
         <v>27593</v>
@@ -30726,22 +30726,22 @@
         <v>58</v>
       </c>
       <c r="O8" t="n">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="P8" t="n">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="Q8" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="R8" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="S8" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="T8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -30894,22 +30894,22 @@
         <v>162</v>
       </c>
       <c r="O10" t="n">
-        <v>2626</v>
+        <v>2609</v>
       </c>
       <c r="P10" t="n">
-        <v>1397</v>
+        <v>1384</v>
       </c>
       <c r="Q10" t="n">
-        <v>1078</v>
+        <v>1068</v>
       </c>
       <c r="R10" t="n">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="S10" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="T10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="U10" t="n">
         <v>2</v>
@@ -30978,25 +30978,25 @@
         <v>48</v>
       </c>
       <c r="O11" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="P11" t="n">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="Q11" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="R11" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="T11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V11" t="n">
         <v>4232</v>
@@ -31146,22 +31146,22 @@
         <v>60</v>
       </c>
       <c r="O13" t="n">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="P13" t="n">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="Q13" t="n">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="R13" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="S13" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="T13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U13" t="n">
         <v>1</v>
@@ -31230,10 +31230,10 @@
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
         <v>3</v>
@@ -31314,25 +31314,25 @@
         <v>497</v>
       </c>
       <c r="O15" t="n">
-        <v>3803</v>
+        <v>3750</v>
       </c>
       <c r="P15" t="n">
-        <v>2107</v>
+        <v>2069</v>
       </c>
       <c r="Q15" t="n">
-        <v>1650</v>
+        <v>1617</v>
       </c>
       <c r="R15" t="n">
-        <v>768</v>
+        <v>748</v>
       </c>
       <c r="S15" t="n">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="T15" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="U15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V15" t="n">
         <v>27231</v>
@@ -31398,22 +31398,22 @@
         <v>122</v>
       </c>
       <c r="O16" t="n">
-        <v>527</v>
+        <v>517</v>
       </c>
       <c r="P16" t="n">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="Q16" t="n">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="R16" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="T16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -33372,25 +33372,25 @@
         <v>9</v>
       </c>
       <c r="O20" t="n">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="P20" t="n">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="Q20" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="R20" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="S20" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="T20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="U20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20" t="n">
         <v>1104</v>
@@ -33456,10 +33456,10 @@
         <v>1</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -33960,25 +33960,25 @@
         <v>27</v>
       </c>
       <c r="O27" t="n">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="P27" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="Q27" t="n">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="R27" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="S27" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="T27" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="U27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V27" t="n">
         <v>490</v>
@@ -34044,25 +34044,25 @@
         <v>8</v>
       </c>
       <c r="O28" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="P28" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q28" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R28" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="S28" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T28" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="U28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V28" t="n">
         <v>294</v>
@@ -34128,25 +34128,25 @@
         <v>205</v>
       </c>
       <c r="O29" t="n">
-        <v>3184</v>
+        <v>3174</v>
       </c>
       <c r="P29" t="n">
-        <v>2537</v>
+        <v>2529</v>
       </c>
       <c r="Q29" t="n">
-        <v>2260</v>
+        <v>2253</v>
       </c>
       <c r="R29" t="n">
-        <v>1603</v>
+        <v>1596</v>
       </c>
       <c r="S29" t="n">
-        <v>1167</v>
+        <v>1160</v>
       </c>
       <c r="T29" t="n">
-        <v>584</v>
+        <v>579</v>
       </c>
       <c r="U29" t="n">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="V29" t="n">
         <v>6931</v>
@@ -34212,25 +34212,25 @@
         <v>125</v>
       </c>
       <c r="O30" t="n">
-        <v>1216</v>
+        <v>1202</v>
       </c>
       <c r="P30" t="n">
-        <v>979</v>
+        <v>970</v>
       </c>
       <c r="Q30" t="n">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="R30" t="n">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="S30" t="n">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="T30" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="U30" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="V30" t="n">
         <v>3042</v>
@@ -34464,22 +34464,22 @@
         <v>457</v>
       </c>
       <c r="O33" t="n">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="P33" t="n">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Q33" t="n">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="R33" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S33" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="T33" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="U33" t="n">
         <v>4</v>
@@ -34716,25 +34716,25 @@
         <v>11644</v>
       </c>
       <c r="O36" t="n">
-        <v>47552</v>
+        <v>46943</v>
       </c>
       <c r="P36" t="n">
-        <v>27622</v>
+        <v>27133</v>
       </c>
       <c r="Q36" t="n">
-        <v>22193</v>
+        <v>21749</v>
       </c>
       <c r="R36" t="n">
-        <v>11714</v>
+        <v>11403</v>
       </c>
       <c r="S36" t="n">
-        <v>7067</v>
+        <v>6838</v>
       </c>
       <c r="T36" t="n">
-        <v>2442</v>
+        <v>2332</v>
       </c>
       <c r="U36" t="n">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="V36" t="n">
         <v>223270</v>
@@ -34800,19 +34800,19 @@
         <v>236</v>
       </c>
       <c r="O37" t="n">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="P37" t="n">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="Q37" t="n">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="R37" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="S37" t="n">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="T37" t="n">
         <v>22</v>
